--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/87.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/87.xlsx
@@ -426,13 +426,13 @@
         <v>-6.759168433036217</v>
       </c>
       <c r="E2">
-        <v>-3.292024872108941</v>
+        <v>-5.065657921588294</v>
       </c>
       <c r="F2">
-        <v>-1.421259093089718</v>
+        <v>-2.570116045460532</v>
       </c>
       <c r="G2">
-        <v>-9.127248700934471</v>
+        <v>-11.123977493153</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.353038006516938</v>
       </c>
       <c r="E3">
-        <v>-3.674975875526081</v>
+        <v>-5.678688525978287</v>
       </c>
       <c r="F3">
-        <v>-1.668101810347734</v>
+        <v>-2.437435610186732</v>
       </c>
       <c r="G3">
-        <v>-8.686779537989384</v>
+        <v>-10.98855294972278</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.763419186294314</v>
       </c>
       <c r="E4">
-        <v>-4.637328931236078</v>
+        <v>-6.902984619945219</v>
       </c>
       <c r="F4">
-        <v>-1.693005019578095</v>
+        <v>-2.462495380856223</v>
       </c>
       <c r="G4">
-        <v>-7.796541739865665</v>
+        <v>-10.31553823918575</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.048515381723558</v>
       </c>
       <c r="E5">
-        <v>-5.61320068980839</v>
+        <v>-6.798165872529196</v>
       </c>
       <c r="F5">
-        <v>-1.427425460036157</v>
+        <v>-2.402589507020569</v>
       </c>
       <c r="G5">
-        <v>-8.293359908693045</v>
+        <v>-9.347436289004374</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.208561793842259</v>
       </c>
       <c r="E6">
-        <v>-6.641315693635721</v>
+        <v>-7.939526489550627</v>
       </c>
       <c r="F6">
-        <v>-0.9775896539873163</v>
+        <v>-2.316270310179249</v>
       </c>
       <c r="G6">
-        <v>-8.10768636411766</v>
+        <v>-8.543633717430938</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.269295126610677</v>
       </c>
       <c r="E7">
-        <v>-7.078474411264524</v>
+        <v>-9.037270081238708</v>
       </c>
       <c r="F7">
-        <v>-1.376830435807969</v>
+        <v>-2.327262745614398</v>
       </c>
       <c r="G7">
-        <v>-7.117488377089395</v>
+        <v>-8.588434094614442</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.23942377647204</v>
       </c>
       <c r="E8">
-        <v>-8.337096796831164</v>
+        <v>-9.435039742662838</v>
       </c>
       <c r="F8">
-        <v>-1.652265082341013</v>
+        <v>-2.20575864333917</v>
       </c>
       <c r="G8">
-        <v>-6.560154454012304</v>
+        <v>-8.038493800219385</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.128299583632698</v>
       </c>
       <c r="E9">
-        <v>-9.067468080781536</v>
+        <v>-10.34083851976264</v>
       </c>
       <c r="F9">
-        <v>-1.588701966421998</v>
+        <v>-2.286835931255574</v>
       </c>
       <c r="G9">
-        <v>-5.763598004051503</v>
+        <v>-6.652744510936136</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.05023141346549486</v>
       </c>
       <c r="E10">
-        <v>-9.230635294100075</v>
+        <v>-11.57951718454746</v>
       </c>
       <c r="F10">
-        <v>-1.036699466748881</v>
+        <v>-2.290318387816943</v>
       </c>
       <c r="G10">
-        <v>-5.397046852714606</v>
+        <v>-5.961928438404605</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.264707638082591</v>
       </c>
       <c r="E11">
-        <v>-9.682483920184797</v>
+        <v>-12.02333349992996</v>
       </c>
       <c r="F11">
-        <v>-1.726848798186872</v>
+        <v>-2.257324514163439</v>
       </c>
       <c r="G11">
-        <v>-3.978715470934265</v>
+        <v>-5.422107390044703</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.470090185253378</v>
       </c>
       <c r="E12">
-        <v>-12.10514760981776</v>
+        <v>-13.22627378126462</v>
       </c>
       <c r="F12">
-        <v>-1.311420060580711</v>
+        <v>-2.311394539646371</v>
       </c>
       <c r="G12">
-        <v>-3.539097410725881</v>
+        <v>-4.649648112659877</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.610732915609636</v>
       </c>
       <c r="E13">
-        <v>-12.20051364825847</v>
+        <v>-13.36162693834078</v>
       </c>
       <c r="F13">
-        <v>-1.090590564872808</v>
+        <v>-2.27303698705974</v>
       </c>
       <c r="G13">
-        <v>-3.120754308190479</v>
+        <v>-3.417843988936216</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>4.620339846964085</v>
       </c>
       <c r="E14">
-        <v>-12.85534632463286</v>
+        <v>-15.00537661005878</v>
       </c>
       <c r="F14">
-        <v>-1.258438509865058</v>
+        <v>-2.227723633391801</v>
       </c>
       <c r="G14">
-        <v>-2.148724492771772</v>
+        <v>-2.764244080551004</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>5.443045484767295</v>
       </c>
       <c r="E15">
-        <v>-15.05113253922441</v>
+        <v>-15.79439539112705</v>
       </c>
       <c r="F15">
-        <v>-1.206369820027289</v>
+        <v>-2.272964090728294</v>
       </c>
       <c r="G15">
-        <v>-1.344690870302022</v>
+        <v>-2.122546556756679</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>6.048440938807597</v>
       </c>
       <c r="E16">
-        <v>-15.45108263659407</v>
+        <v>-17.13969529704286</v>
       </c>
       <c r="F16">
-        <v>-0.8724184717930855</v>
+        <v>-2.134268051375364</v>
       </c>
       <c r="G16">
-        <v>-1.09270702385695</v>
+        <v>-1.51749605478781</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>6.436052972736272</v>
       </c>
       <c r="E17">
-        <v>-15.25658359704103</v>
+        <v>-18.17131976443967</v>
       </c>
       <c r="F17">
-        <v>-1.137894485409674</v>
+        <v>-1.854699851502351</v>
       </c>
       <c r="G17">
-        <v>-0.002112853577423725</v>
+        <v>-0.8863563821199469</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.629715965352701</v>
       </c>
       <c r="E18">
-        <v>-16.26828926292396</v>
+        <v>-18.91961630846801</v>
       </c>
       <c r="F18">
-        <v>-0.9683956041836446</v>
+        <v>-1.667163270080362</v>
       </c>
       <c r="G18">
-        <v>0.05118027576097178</v>
+        <v>-1.024339455249466</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.671075050874538</v>
       </c>
       <c r="E19">
-        <v>-18.083587328414</v>
+        <v>-19.46884528048598</v>
       </c>
       <c r="F19">
-        <v>-0.4682248812710947</v>
+        <v>-1.740821699537294</v>
       </c>
       <c r="G19">
-        <v>0.0935343852626026</v>
+        <v>-0.4777565783985799</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.608750511346795</v>
       </c>
       <c r="E20">
-        <v>-17.93886867980035</v>
+        <v>-20.35232885313749</v>
       </c>
       <c r="F20">
-        <v>-0.9195799131366698</v>
+        <v>-1.767307918874405</v>
       </c>
       <c r="G20">
-        <v>-0.3055727511254765</v>
+        <v>-0.5726467013071834</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.482662670105658</v>
       </c>
       <c r="E21">
-        <v>-18.98586418231035</v>
+        <v>-21.45140977887216</v>
       </c>
       <c r="F21">
-        <v>-0.4300031809385227</v>
+        <v>-1.370274736182214</v>
       </c>
       <c r="G21">
-        <v>-0.01063954541199972</v>
+        <v>-0.0560090649163664</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.321956611109261</v>
       </c>
       <c r="E22">
-        <v>-19.94890251788894</v>
+        <v>-21.58632684875922</v>
       </c>
       <c r="F22">
-        <v>0.2892798320559272</v>
+        <v>-1.349645074382895</v>
       </c>
       <c r="G22">
-        <v>0.1037006247003977</v>
+        <v>-0.3135537973405098</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.145346514514077</v>
       </c>
       <c r="E23">
-        <v>-20.3035037008028</v>
+        <v>-22.35180522803837</v>
       </c>
       <c r="F23">
-        <v>-0.06351687459196545</v>
+        <v>-1.362469858513037</v>
       </c>
       <c r="G23">
-        <v>-0.6610752313527815</v>
+        <v>0.09339340505468249</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.965458076064087</v>
       </c>
       <c r="E24">
-        <v>-20.73044551857253</v>
+        <v>-22.85270327986931</v>
       </c>
       <c r="F24">
-        <v>0.3815839833824733</v>
+        <v>-1.110773736642018</v>
       </c>
       <c r="G24">
-        <v>0.2307237920364235</v>
+        <v>-0.2597750695081673</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.78903175401878</v>
       </c>
       <c r="E25">
-        <v>-20.2618511444261</v>
+        <v>-23.25370413970416</v>
       </c>
       <c r="F25">
-        <v>0.2378001114415491</v>
+        <v>-1.230646783501135</v>
       </c>
       <c r="G25">
-        <v>0.662841183034539</v>
+        <v>-0.1288201208179248</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.619007935300095</v>
       </c>
       <c r="E26">
-        <v>-21.5541560738371</v>
+        <v>-22.80658186810709</v>
       </c>
       <c r="F26">
-        <v>0.2346498302087026</v>
+        <v>-1.050440425226519</v>
       </c>
       <c r="G26">
-        <v>0.7039943500242578</v>
+        <v>-0.7743606606503692</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.456461707210861</v>
       </c>
       <c r="E27">
-        <v>-21.6769706859236</v>
+        <v>-23.69493300443129</v>
       </c>
       <c r="F27">
-        <v>0.3417428247774283</v>
+        <v>-0.967510079430052</v>
       </c>
       <c r="G27">
-        <v>0.03382404571925066</v>
+        <v>-0.4868106406405608</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.303186773227694</v>
       </c>
       <c r="E28">
-        <v>-20.99730595903806</v>
+        <v>-22.804509415656</v>
       </c>
       <c r="F28">
-        <v>-0.007716389604585147</v>
+        <v>-1.117765157521646</v>
       </c>
       <c r="G28">
-        <v>-0.3359461536984885</v>
+        <v>-0.6903364567299792</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.167006294221947</v>
       </c>
       <c r="E29">
-        <v>-21.08670383280499</v>
+        <v>-22.90022017063668</v>
       </c>
       <c r="F29">
-        <v>0.3962601686578722</v>
+        <v>-1.098855186450539</v>
       </c>
       <c r="G29">
-        <v>-0.3561428738553408</v>
+        <v>-0.7369617443826714</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.054910360550691</v>
       </c>
       <c r="E30">
-        <v>-20.86173683497301</v>
+        <v>-23.06600806030118</v>
       </c>
       <c r="F30">
-        <v>0.643885693111534</v>
+        <v>-0.8751106658521839</v>
       </c>
       <c r="G30">
-        <v>-0.3529238257744982</v>
+        <v>-0.8395326778783302</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.97487408672194</v>
       </c>
       <c r="E31">
-        <v>-20.85583927489175</v>
+        <v>-22.25081989467516</v>
       </c>
       <c r="F31">
-        <v>0.1666267841930156</v>
+        <v>-0.8347418372115556</v>
       </c>
       <c r="G31">
-        <v>-0.589138774889246</v>
+        <v>-1.042411029309152</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.932938901694223</v>
       </c>
       <c r="E32">
-        <v>-21.20921110725346</v>
+        <v>-22.43756488868475</v>
       </c>
       <c r="F32">
-        <v>0.2609894285155185</v>
+        <v>-0.6526037261536115</v>
       </c>
       <c r="G32">
-        <v>-0.4731642786628116</v>
+        <v>-0.9899637812182777</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.935345316362454</v>
       </c>
       <c r="E33">
-        <v>-19.91313921517084</v>
+        <v>-22.05978048015569</v>
       </c>
       <c r="F33">
-        <v>-0.02796500239861626</v>
+        <v>-0.7870311882799153</v>
       </c>
       <c r="G33">
-        <v>-0.3940247778723946</v>
+        <v>-1.445395121415035</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.983077435733013</v>
       </c>
       <c r="E34">
-        <v>-19.75136332764612</v>
+        <v>-21.77514014200857</v>
       </c>
       <c r="F34">
-        <v>0.5916372475473579</v>
+        <v>-0.7784642126001627</v>
       </c>
       <c r="G34">
-        <v>-1.644386074149689</v>
+        <v>-1.230170558812838</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.075893850003079</v>
       </c>
       <c r="E35">
-        <v>-19.39817838979403</v>
+        <v>-20.87463670934792</v>
       </c>
       <c r="F35">
-        <v>0.3092525985048261</v>
+        <v>-0.8413397835748536</v>
       </c>
       <c r="G35">
-        <v>-1.121626241692712</v>
+        <v>-1.285763754136004</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.208637438109737</v>
       </c>
       <c r="E36">
-        <v>-18.91637265042332</v>
+        <v>-20.29465320746959</v>
       </c>
       <c r="F36">
-        <v>0.3348342406380804</v>
+        <v>-0.5146656429742434</v>
       </c>
       <c r="G36">
-        <v>-1.188341208974021</v>
+        <v>-1.418817741477502</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.371049752935358</v>
       </c>
       <c r="E37">
-        <v>-17.12158729566661</v>
+        <v>-20.53534011016605</v>
       </c>
       <c r="F37">
-        <v>0.3728753568768421</v>
+        <v>-0.6757093781198981</v>
       </c>
       <c r="G37">
-        <v>-1.383588353965019</v>
+        <v>-1.352178485789335</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.546115977404906</v>
       </c>
       <c r="E38">
-        <v>-16.89920774848999</v>
+        <v>-19.18095713108284</v>
       </c>
       <c r="F38">
-        <v>0.3405922224549398</v>
+        <v>-0.5675254236816855</v>
       </c>
       <c r="G38">
-        <v>-1.400012548187713</v>
+        <v>-1.518391540182562</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.71326108101935</v>
       </c>
       <c r="E39">
-        <v>-17.14494495615745</v>
+        <v>-18.59197362026361</v>
       </c>
       <c r="F39">
-        <v>0.4958713488445127</v>
+        <v>-0.5512496609514808</v>
       </c>
       <c r="G39">
-        <v>-0.9463277961224102</v>
+        <v>-1.576585037118477</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.849141457969539</v>
       </c>
       <c r="E40">
-        <v>-15.36105347470577</v>
+        <v>-17.65541616009212</v>
       </c>
       <c r="F40">
-        <v>0.4741714363607769</v>
+        <v>-0.4908103185084232</v>
       </c>
       <c r="G40">
-        <v>-0.6780137422599245</v>
+        <v>-1.916642352344756</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.93219226744705</v>
       </c>
       <c r="E41">
-        <v>-15.7677400808443</v>
+        <v>-17.80944630849604</v>
       </c>
       <c r="F41">
-        <v>0.5362186399326683</v>
+        <v>-0.3254176544980711</v>
       </c>
       <c r="G41">
-        <v>-1.585255319905565</v>
+        <v>-2.494849178427798</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.946663050780992</v>
       </c>
       <c r="E42">
-        <v>-15.7555960909305</v>
+        <v>-16.93004118936552</v>
       </c>
       <c r="F42">
-        <v>0.6876574550428627</v>
+        <v>-0.5929165413122959</v>
       </c>
       <c r="G42">
-        <v>-1.531899532696982</v>
+        <v>-2.044138064451773</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.880973877851807</v>
       </c>
       <c r="E43">
-        <v>-15.37203041223729</v>
+        <v>-15.49858706772746</v>
       </c>
       <c r="F43">
-        <v>0.5969976130108735</v>
+        <v>-0.4353320684407319</v>
       </c>
       <c r="G43">
-        <v>-2.289059846777884</v>
+        <v>-2.31421176016867</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.732117447182877</v>
       </c>
       <c r="E44">
-        <v>-13.64473474150905</v>
+        <v>-15.48535078323524</v>
       </c>
       <c r="F44">
-        <v>0.5843277335850551</v>
+        <v>-0.261258114049041</v>
       </c>
       <c r="G44">
-        <v>-1.571974462170571</v>
+        <v>-2.742042308548177</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.503382369737956</v>
       </c>
       <c r="E45">
-        <v>-12.16546885109957</v>
+        <v>-14.44031559647055</v>
       </c>
       <c r="F45">
-        <v>0.4275873670969438</v>
+        <v>-0.2698085223807375</v>
       </c>
       <c r="G45">
-        <v>-2.018067168964916</v>
+        <v>-2.516024927806318</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.205156309958848</v>
       </c>
       <c r="E46">
-        <v>-11.58987529359158</v>
+        <v>-12.9421692073784</v>
       </c>
       <c r="F46">
-        <v>0.9893745425319294</v>
+        <v>-0.2863651016604912</v>
       </c>
       <c r="G46">
-        <v>-2.144706556846049</v>
+        <v>-2.778788538668096</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.851325977285974</v>
       </c>
       <c r="E47">
-        <v>-11.44622402028841</v>
+        <v>-12.88210961841006</v>
       </c>
       <c r="F47">
-        <v>0.4583139991689859</v>
+        <v>0.06087574481682512</v>
       </c>
       <c r="G47">
-        <v>-2.260046642136842</v>
+        <v>-3.183044063389851</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.460502946069611</v>
       </c>
       <c r="E48">
-        <v>-10.3212104430415</v>
+        <v>-12.27370984464725</v>
       </c>
       <c r="F48">
-        <v>0.613914532110845</v>
+        <v>-0.3349944100418362</v>
       </c>
       <c r="G48">
-        <v>-2.631385899053841</v>
+        <v>-3.399858569448036</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.050608522669721</v>
       </c>
       <c r="E49">
-        <v>-11.33531251185886</v>
+        <v>-10.98167072076104</v>
       </c>
       <c r="F49">
-        <v>0.3439330281904302</v>
+        <v>-0.1549421281041413</v>
       </c>
       <c r="G49">
-        <v>-2.006799195309671</v>
+        <v>-3.887201040781971</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.63715730195159</v>
       </c>
       <c r="E50">
-        <v>-10.08569844165578</v>
+        <v>-10.50353642020148</v>
       </c>
       <c r="F50">
-        <v>0.7366794095731346</v>
+        <v>-0.09905963474388384</v>
       </c>
       <c r="G50">
-        <v>-2.387829536148882</v>
+        <v>-4.010516950798616</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.234162394934951</v>
       </c>
       <c r="E51">
-        <v>-8.621355039536404</v>
+        <v>-9.54795309895095</v>
       </c>
       <c r="F51">
-        <v>0.7139481796729134</v>
+        <v>-0.251210017453083</v>
       </c>
       <c r="G51">
-        <v>-2.436446821924594</v>
+        <v>-3.996254453097364</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.852420866776699</v>
       </c>
       <c r="E52">
-        <v>-9.013056859214958</v>
+        <v>-8.685019615934701</v>
       </c>
       <c r="F52">
-        <v>0.09179372975891387</v>
+        <v>-0.3411193586181357</v>
       </c>
       <c r="G52">
-        <v>-3.175123064300413</v>
+        <v>-4.770460318613645</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.496954799794877</v>
       </c>
       <c r="E53">
-        <v>-8.961723167240077</v>
+        <v>-7.905677817253274</v>
       </c>
       <c r="F53">
-        <v>0.2893129667520392</v>
+        <v>-0.4856462761193711</v>
       </c>
       <c r="G53">
-        <v>-3.216406768519688</v>
+        <v>-4.743512212944173</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.167694599467298</v>
       </c>
       <c r="E54">
-        <v>-6.869862759629711</v>
+        <v>-7.680312111134103</v>
       </c>
       <c r="F54">
-        <v>0.1540240025268239</v>
+        <v>-0.03407172689205422</v>
       </c>
       <c r="G54">
-        <v>-3.495497976054289</v>
+        <v>-5.121550640481968</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.864640936574596</v>
       </c>
       <c r="E55">
-        <v>-7.365261959666584</v>
+        <v>-7.144871800714558</v>
       </c>
       <c r="F55">
-        <v>0.3264428788477214</v>
+        <v>-0.09284687922288754</v>
       </c>
       <c r="G55">
-        <v>-4.738677113961431</v>
+        <v>-5.218466701193275</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.585708142022098</v>
       </c>
       <c r="E56">
-        <v>-6.221874575518637</v>
+        <v>-6.442750660195668</v>
       </c>
       <c r="F56">
-        <v>0.2952573312345284</v>
+        <v>-0.2320051475865793</v>
       </c>
       <c r="G56">
-        <v>-3.480606288906579</v>
+        <v>-5.562199944803842</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.328566199283901</v>
       </c>
       <c r="E57">
-        <v>-5.744832569537506</v>
+        <v>-5.528093083340003</v>
       </c>
       <c r="F57">
-        <v>0.618125123619275</v>
+        <v>-0.118903175877946</v>
       </c>
       <c r="G57">
-        <v>-4.597072938084038</v>
+        <v>-5.567366608349655</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.091975262932798</v>
       </c>
       <c r="E58">
-        <v>-5.241596259730681</v>
+        <v>-5.527848043871839</v>
       </c>
       <c r="F58">
-        <v>0.274505899426998</v>
+        <v>-0.1352824845335006</v>
       </c>
       <c r="G58">
-        <v>-5.121610687607563</v>
+        <v>-6.133237666239686</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.8780333050038672</v>
       </c>
       <c r="E59">
-        <v>-5.041768650047881</v>
+        <v>-4.461706237154377</v>
       </c>
       <c r="F59">
-        <v>0.6146310699142666</v>
+        <v>-0.1614862305862574</v>
       </c>
       <c r="G59">
-        <v>-4.161846150277906</v>
+        <v>-5.746045968165448</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.6864667161347991</v>
       </c>
       <c r="E60">
-        <v>-3.340181357420328</v>
+        <v>-3.859154184936928</v>
       </c>
       <c r="F60">
-        <v>0.192389838787483</v>
+        <v>-0.3492050528368618</v>
       </c>
       <c r="G60">
-        <v>-5.006978114100962</v>
+        <v>-6.288185357722259</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.5146030616005847</v>
       </c>
       <c r="E61">
-        <v>-4.301674698386084</v>
+        <v>-3.448750454662671</v>
       </c>
       <c r="F61">
-        <v>0.02216033751218462</v>
+        <v>-0.3078736612741804</v>
       </c>
       <c r="G61">
-        <v>-4.901383938368793</v>
+        <v>-6.62212569837156</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.3580599913026189</v>
       </c>
       <c r="E62">
-        <v>-3.108394786592972</v>
+        <v>-3.284391269693906</v>
       </c>
       <c r="F62">
-        <v>0.02954688964294781</v>
+        <v>-0.2517501129997083</v>
       </c>
       <c r="G62">
-        <v>-4.492590939547684</v>
+        <v>-6.272828958037332</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.2116748136261978</v>
       </c>
       <c r="E63">
-        <v>-2.309620112122673</v>
+        <v>-2.532435746488399</v>
       </c>
       <c r="F63">
-        <v>0.3751376282538876</v>
+        <v>-0.1127036742353945</v>
       </c>
       <c r="G63">
-        <v>-5.129474250315996</v>
+        <v>-6.809321307043565</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.06861584106269322</v>
       </c>
       <c r="E64">
-        <v>-1.941018453832815</v>
+        <v>-2.579022317919001</v>
       </c>
       <c r="F64">
-        <v>0.4240104766516556</v>
+        <v>-0.4315704520646194</v>
       </c>
       <c r="G64">
-        <v>-5.846457815884256</v>
+        <v>-6.299844943066172</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.08121406702519533</v>
       </c>
       <c r="E65">
-        <v>-2.410406091342287</v>
+        <v>-1.695007134217921</v>
       </c>
       <c r="F65">
-        <v>-0.1113592339406509</v>
+        <v>-0.3431753665118841</v>
       </c>
       <c r="G65">
-        <v>-4.694320563358416</v>
+        <v>-7.06007027129704</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.2468158089537459</v>
       </c>
       <c r="E66">
-        <v>-3.037902330776657</v>
+        <v>-1.58202732654861</v>
       </c>
       <c r="F66">
-        <v>-0.5972497311963401</v>
+        <v>-0.2627889370094145</v>
       </c>
       <c r="G66">
-        <v>-5.1627586331081</v>
+        <v>-6.332092860255603</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.434665050947704</v>
       </c>
       <c r="E67">
-        <v>-2.907969114479396</v>
+        <v>-0.9422791137059962</v>
       </c>
       <c r="F67">
-        <v>0.5277113067059173</v>
+        <v>-0.7228824166071215</v>
       </c>
       <c r="G67">
-        <v>-5.483874996325852</v>
+        <v>-7.014797349342545</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.6493699879467409</v>
       </c>
       <c r="E68">
-        <v>-2.12147963910794</v>
+        <v>-1.446362678623086</v>
       </c>
       <c r="F68">
-        <v>-0.1223226765167024</v>
+        <v>-0.3528374438981376</v>
       </c>
       <c r="G68">
-        <v>-5.717925638174567</v>
+        <v>-7.047977302351003</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.8963089653786684</v>
       </c>
       <c r="E69">
-        <v>-1.35747980306043</v>
+        <v>-1.084244183211285</v>
       </c>
       <c r="F69">
-        <v>-0.07843742825119014</v>
+        <v>-0.5211583866773859</v>
       </c>
       <c r="G69">
-        <v>-5.39353801198415</v>
+        <v>-6.993060289876936</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.176584596292842</v>
       </c>
       <c r="E70">
-        <v>-0.3923856278760476</v>
+        <v>-1.233876080822208</v>
       </c>
       <c r="F70">
-        <v>-0.1831894565396044</v>
+        <v>-0.6034160981427796</v>
       </c>
       <c r="G70">
-        <v>-5.003046332746745</v>
+        <v>-6.442026093498201</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.486247171167274</v>
       </c>
       <c r="E71">
-        <v>-1.216096183140617</v>
+        <v>-0.9568195065542209</v>
       </c>
       <c r="F71">
-        <v>0.2324679104697287</v>
+        <v>-0.2659234792616079</v>
       </c>
       <c r="G71">
-        <v>-5.247693986890789</v>
+        <v>-6.915335812654902</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.816975581564054</v>
       </c>
       <c r="E72">
-        <v>-1.122578323739453</v>
+        <v>-0.9785491082057238</v>
       </c>
       <c r="F72">
-        <v>-0.1535131943343121</v>
+        <v>-0.3597211770154015</v>
       </c>
       <c r="G72">
-        <v>-5.710401472262978</v>
+        <v>-6.447939429997072</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.156480076975928</v>
       </c>
       <c r="E73">
-        <v>-2.291516263957745</v>
+        <v>-1.213076798507467</v>
       </c>
       <c r="F73">
-        <v>-0.1909454605320162</v>
+        <v>-0.4438352598304688</v>
       </c>
       <c r="G73">
-        <v>-5.846763273001416</v>
+        <v>-6.000123631772593</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.490194150980349</v>
       </c>
       <c r="E74">
-        <v>-2.287740994863476</v>
+        <v>-1.686854380387283</v>
       </c>
       <c r="F74">
-        <v>-0.3755753007375812</v>
+        <v>-0.2916343467096989</v>
       </c>
       <c r="G74">
-        <v>-4.627477669592143</v>
+        <v>-6.399040183805521</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.803864887973001</v>
       </c>
       <c r="E75">
-        <v>-2.281415654015762</v>
+        <v>-1.648125684783257</v>
       </c>
       <c r="F75">
-        <v>-0.6627255474484186</v>
+        <v>-0.5056969091041331</v>
       </c>
       <c r="G75">
-        <v>-5.233269623024888</v>
+        <v>-5.938014017950008</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.086746765264436</v>
       </c>
       <c r="E76">
-        <v>-3.286214529465506</v>
+        <v>-2.435616084083996</v>
       </c>
       <c r="F76">
-        <v>-0.3395943342295819</v>
+        <v>-0.5618519353399116</v>
       </c>
       <c r="G76">
-        <v>-4.335515491223354</v>
+        <v>-6.163752049020618</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.328898792567644</v>
       </c>
       <c r="E77">
-        <v>-3.634016905440622</v>
+        <v>-3.255659353748742</v>
       </c>
       <c r="F77">
-        <v>-0.1009168344609603</v>
+        <v>-0.5462753146976698</v>
       </c>
       <c r="G77">
-        <v>-3.806492482492295</v>
+        <v>-5.777933602601306</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.521205081031961</v>
       </c>
       <c r="E78">
-        <v>-3.310963515750159</v>
+        <v>-3.524430271423697</v>
       </c>
       <c r="F78">
-        <v>-0.4172769725293139</v>
+        <v>-0.45135435074568</v>
       </c>
       <c r="G78">
-        <v>-4.260597564436766</v>
+        <v>-5.361861847860173</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.655868824083872</v>
       </c>
       <c r="E79">
-        <v>-5.772372513832444</v>
+        <v>-4.053291895104714</v>
       </c>
       <c r="F79">
-        <v>-0.4499113347300032</v>
+        <v>-0.3443516482238594</v>
       </c>
       <c r="G79">
-        <v>-3.811536441042326</v>
+        <v>-5.137191611327328</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.729187060190986</v>
       </c>
       <c r="E80">
-        <v>-5.01066525043624</v>
+        <v>-4.049230054429031</v>
       </c>
       <c r="F80">
-        <v>-0.3890172185828088</v>
+        <v>-0.405452027854351</v>
       </c>
       <c r="G80">
-        <v>-3.496247259751939</v>
+        <v>-4.461034869674898</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.740636703956434</v>
       </c>
       <c r="E81">
-        <v>-6.144840811865717</v>
+        <v>-4.79532124324388</v>
       </c>
       <c r="F81">
-        <v>-0.202969213383651</v>
+        <v>-0.2562614018753544</v>
       </c>
       <c r="G81">
-        <v>-3.442311887244129</v>
+        <v>-4.715350111039834</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.695558794342105</v>
       </c>
       <c r="E82">
-        <v>-7.420649185894498</v>
+        <v>-6.117500221714371</v>
       </c>
       <c r="F82">
-        <v>-0.2582113787415444</v>
+        <v>-0.5020139876312866</v>
       </c>
       <c r="G82">
-        <v>-3.045726730131066</v>
+        <v>-4.5005772072519</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.602914376682608</v>
       </c>
       <c r="E83">
-        <v>-8.164746833273428</v>
+        <v>-7.169658165901135</v>
       </c>
       <c r="F83">
-        <v>-0.7127200053095772</v>
+        <v>-0.210782374726856</v>
       </c>
       <c r="G83">
-        <v>-3.047314062842462</v>
+        <v>-4.053223510820047</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.472690970240189</v>
       </c>
       <c r="E84">
-        <v>-9.207177956537445</v>
+        <v>-8.423487745598923</v>
       </c>
       <c r="F84">
-        <v>-0.1581006930110158</v>
+        <v>-0.4003144932221884</v>
       </c>
       <c r="G84">
-        <v>-2.84596038625285</v>
+        <v>-3.924897581933056</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.317737430458714</v>
       </c>
       <c r="E85">
-        <v>-9.846801573040313</v>
+        <v>-10.26283705787104</v>
       </c>
       <c r="F85">
-        <v>-0.3525127238762402</v>
+        <v>-0.2213747087064532</v>
       </c>
       <c r="G85">
-        <v>-3.07521509028769</v>
+        <v>-3.581151284599534</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.154457264978312</v>
       </c>
       <c r="E86">
-        <v>-11.34030051865998</v>
+        <v>-10.70505854010481</v>
       </c>
       <c r="F86">
-        <v>-0.9022264444154229</v>
+        <v>-0.4113384066186442</v>
       </c>
       <c r="G86">
-        <v>-2.738948576207708</v>
+        <v>-3.545987165701829</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.003997595338543</v>
       </c>
       <c r="E87">
-        <v>-12.40193193787868</v>
+        <v>-12.69744953648553</v>
       </c>
       <c r="F87">
-        <v>0.02083991987212221</v>
+        <v>-0.3657036463984195</v>
       </c>
       <c r="G87">
-        <v>-2.430486492023082</v>
+        <v>-3.170737013387343</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.888271549802262</v>
       </c>
       <c r="E88">
-        <v>-15.53636052472678</v>
+        <v>-14.41537140925363</v>
       </c>
       <c r="F88">
-        <v>-0.2241671352212904</v>
+        <v>-0.366767270143614</v>
       </c>
       <c r="G88">
-        <v>-2.105686368187269</v>
+        <v>-3.321554506926775</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.829982569616292</v>
       </c>
       <c r="E89">
-        <v>-15.51191472286884</v>
+        <v>-15.38878446672165</v>
       </c>
       <c r="F89">
-        <v>-0.5046250016849105</v>
+        <v>-0.1878216870560593</v>
       </c>
       <c r="G89">
-        <v>-2.845370357975259</v>
+        <v>-3.024075825236963</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.849148034077056</v>
       </c>
       <c r="E90">
-        <v>-17.28142363350264</v>
+        <v>-17.18612819965445</v>
       </c>
       <c r="F90">
-        <v>-0.3742432859538796</v>
+        <v>-0.3938697948284083</v>
       </c>
       <c r="G90">
-        <v>-1.883947997830244</v>
+        <v>-2.288469818500293</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.962520408766236</v>
       </c>
       <c r="E91">
-        <v>-20.22463006453298</v>
+        <v>-19.08076506108268</v>
       </c>
       <c r="F91">
-        <v>-0.1441087392103294</v>
+        <v>-0.2863096010445037</v>
       </c>
       <c r="G91">
-        <v>-1.688768732198615</v>
+        <v>-2.740841366036265</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.178505939998656</v>
       </c>
       <c r="E92">
-        <v>-21.19006064983468</v>
+        <v>-20.76257891459272</v>
       </c>
       <c r="F92">
-        <v>-0.5015045416785648</v>
+        <v>-0.2723880584730552</v>
       </c>
       <c r="G92">
-        <v>-1.998032314972713</v>
+        <v>-2.922092309274305</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.498757312938566</v>
       </c>
       <c r="E93">
-        <v>-22.55350593602866</v>
+        <v>-23.48790787952256</v>
       </c>
       <c r="F93">
-        <v>-0.1361423298976065</v>
+        <v>-0.4063350675057352</v>
       </c>
       <c r="G93">
-        <v>-1.42151202989553</v>
+        <v>-2.705893938939623</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.911447996648628</v>
       </c>
       <c r="E94">
-        <v>-26.78899237720206</v>
+        <v>-25.77597014332915</v>
       </c>
       <c r="F94">
-        <v>-0.4998834266712862</v>
+        <v>-0.2639660470887926</v>
       </c>
       <c r="G94">
-        <v>-2.525799555555446</v>
+        <v>-2.949640886199732</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.395784691352857</v>
       </c>
       <c r="E95">
-        <v>-28.56189238488258</v>
+        <v>-28.48802129165352</v>
       </c>
       <c r="F95">
-        <v>-0.38554967263469</v>
+        <v>-0.4593058494451524</v>
       </c>
       <c r="G95">
-        <v>-2.554778820516803</v>
+        <v>-2.910581536372086</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.919160805139914</v>
       </c>
       <c r="E96">
-        <v>-30.99356023666777</v>
+        <v>-30.52100785212878</v>
       </c>
       <c r="F96">
-        <v>-0.5086376133840714</v>
+        <v>-0.3134949624695779</v>
       </c>
       <c r="G96">
-        <v>-2.581249159926101</v>
+        <v>-2.971978416921297</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.443319171604013</v>
       </c>
       <c r="E97">
-        <v>-33.60446199978159</v>
+        <v>-33.45480518290272</v>
       </c>
       <c r="F97">
-        <v>-0.4565101094607041</v>
+        <v>-0.4922831557506007</v>
       </c>
       <c r="G97">
-        <v>-3.308265816958009</v>
+        <v>-3.312228927247319</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.927872549335715</v>
       </c>
       <c r="E98">
-        <v>-35.8393008604605</v>
+        <v>-35.6505124864791</v>
       </c>
       <c r="F98">
-        <v>-0.1708326999920442</v>
+        <v>-0.5359646256350242</v>
       </c>
       <c r="G98">
-        <v>-3.296512244808817</v>
+        <v>-3.222468917460253</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.339538186702999</v>
       </c>
       <c r="E99">
-        <v>-38.55880702311293</v>
+        <v>-38.19922198660928</v>
       </c>
       <c r="F99">
-        <v>-0.9125868355222363</v>
+        <v>-0.4344523422589588</v>
       </c>
       <c r="G99">
-        <v>-2.296672778005571</v>
+        <v>-3.559163593653178</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.65178986971923</v>
       </c>
       <c r="E100">
-        <v>-41.37071590792581</v>
+        <v>-40.52761400898562</v>
       </c>
       <c r="F100">
-        <v>-0.2744109316706916</v>
+        <v>-0.5043938871795295</v>
       </c>
       <c r="G100">
-        <v>-3.092211037575838</v>
+        <v>-3.554482528601312</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.852694422548116</v>
       </c>
       <c r="E101">
-        <v>-44.75319296454364</v>
+        <v>-43.23599164189317</v>
       </c>
       <c r="F101">
-        <v>-0.9166582613069959</v>
+        <v>-0.7507776888963948</v>
       </c>
       <c r="G101">
-        <v>-3.050715863044683</v>
+        <v>-3.854746874769841</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.938223768077473</v>
       </c>
       <c r="E102">
-        <v>-46.62107691522299</v>
+        <v>-45.4674041032291</v>
       </c>
       <c r="F102">
-        <v>-0.988308728179542</v>
+        <v>-0.9057834540430439</v>
       </c>
       <c r="G102">
-        <v>-3.775419400368865</v>
+        <v>-4.285303040502471</v>
       </c>
     </row>
   </sheetData>
